--- a/Result/profitability/2501.xlsx
+++ b/Result/profitability/2501.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.59</v>
+        <v>0.60875</v>
       </c>
       <c r="N2" t="n">
-        <v>25.6325</v>
+        <v>26.435</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>0.595</v>
+        <v>0.5575</v>
       </c>
       <c r="N3" t="n">
-        <v>27.92</v>
+        <v>28.64625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0.54625</v>
+        <v>0.5525</v>
       </c>
       <c r="N4" t="n">
-        <v>27.24875</v>
+        <v>28.54875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5125000000000001</v>
+        <v>0.3875</v>
       </c>
       <c r="N5" t="n">
-        <v>24.4475</v>
+        <v>23.2725</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.365</v>
+        <v>0.32625</v>
       </c>
       <c r="N6" t="n">
-        <v>21.78125</v>
+        <v>21.74125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3025</v>
+        <v>0.215</v>
       </c>
       <c r="N7" t="n">
-        <v>20.3275</v>
+        <v>20.52125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2</v>
+        <v>0.07625</v>
       </c>
       <c r="N8" t="n">
-        <v>19.785</v>
+        <v>20.27375</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3285</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2363</v>
+      </c>
+      <c r="E75" t="n">
+        <v>922</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="G75" t="n">
+        <v>362</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>366</v>
+      </c>
+      <c r="K75" t="n">
+        <v>256</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.76375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8181818181818181</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.161904761904762</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.819672131147541</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-9.400000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2509343299519488</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
